--- a/outputs_xlsx_solution/test_1.1-wide.xlsx
+++ b/outputs_xlsx_solution/test_1.1-wide.xlsx
@@ -59,13 +59,16 @@
     <t>fld F2, 104(X0)</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
   </si>
   <si>
     <t>fld F3, 108(X0)</t>
   </si>
   <si>
-    <t>WB/CT</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>fld F4, 112(X0)</t>
@@ -83,9 +86,6 @@
     <t>fmul F8, F2, F3</t>
   </si>
   <si>
-    <t>EX</t>
-  </si>
-  <si>
     <t>fsub F9, F6, F3</t>
   </si>
   <si>
@@ -101,9 +101,15 @@
     <t>fsd F8, 132(X0)</t>
   </si>
   <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
     <t>fsd F9, 136(X0)</t>
   </si>
   <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
     <t>fsd F10, 140(X0)</t>
   </si>
   <si>
@@ -116,13 +122,31 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>IS</t>
+  </si>
+  <si>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -552,6 +576,15 @@
       <c r="X1">
         <v>21</v>
       </c>
+      <c r="Y1">
+        <v>22</v>
+      </c>
+      <c r="Z1">
+        <v>23</v>
+      </c>
+      <c r="AA1">
+        <v>24</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -573,7 +606,7 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -619,7 +652,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -630,7 +663,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>5</v>
@@ -642,7 +675,7 @@
         <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -653,7 +686,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
@@ -665,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -676,7 +709,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
         <v>5</v>
@@ -688,13 +721,13 @@
         <v>8</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M7" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -705,7 +738,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
         <v>5</v>
@@ -717,13 +750,13 @@
         <v>8</v>
       </c>
       <c r="M8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -734,7 +767,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
@@ -746,19 +779,19 @@
         <v>8</v>
       </c>
       <c r="N9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="R9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -781,16 +814,16 @@
         <v>8</v>
       </c>
       <c r="O10" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P10" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="s">
         <v>10</v>
       </c>
-      <c r="R10" t="s">
-        <v>10</v>
+      <c r="S10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -813,28 +846,22 @@
         <v>8</v>
       </c>
       <c r="P11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="U11" t="s">
-        <v>16</v>
-      </c>
-      <c r="V11" t="s">
-        <v>16</v>
-      </c>
-      <c r="W11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -857,10 +884,16 @@
         <v>8</v>
       </c>
       <c r="Q12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R12" t="s">
+        <v>22</v>
+      </c>
+      <c r="S12" t="s">
         <v>10</v>
       </c>
-      <c r="W12" t="s">
-        <v>10</v>
+      <c r="V12" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -883,10 +916,25 @@
         <v>8</v>
       </c>
       <c r="R13" t="s">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="S13" t="s">
+        <v>22</v>
+      </c>
+      <c r="T13" t="s">
+        <v>22</v>
+      </c>
+      <c r="U13" t="s">
+        <v>22</v>
+      </c>
+      <c r="V13" t="s">
+        <v>22</v>
       </c>
       <c r="W13" t="s">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="X13" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -906,13 +954,16 @@
         <v>6</v>
       </c>
       <c r="R14" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="S14" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" t="s">
         <v>10</v>
       </c>
-      <c r="W14" t="s">
-        <v>10</v>
+      <c r="Y14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -923,7 +974,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q15" t="s">
         <v>5</v>
@@ -931,14 +982,17 @@
       <c r="R15" t="s">
         <v>6</v>
       </c>
-      <c r="S15" t="s">
-        <v>8</v>
-      </c>
       <c r="T15" t="s">
+        <v>8</v>
+      </c>
+      <c r="U15" t="s">
+        <v>22</v>
+      </c>
+      <c r="V15" t="s">
         <v>10</v>
       </c>
-      <c r="W15" t="s">
-        <v>10</v>
+      <c r="Z15" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -949,7 +1003,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R16" t="s">
         <v>5</v>
@@ -957,19 +1011,22 @@
       <c r="S16" t="s">
         <v>6</v>
       </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
+        <v>24</v>
+      </c>
+      <c r="V16" t="s">
         <v>8</v>
       </c>
       <c r="W16" t="s">
-        <v>16</v>
-      </c>
-      <c r="X16" t="s">
         <v>10</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -977,7 +1034,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -985,23 +1042,23 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -1009,7 +1066,31 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/test_1.1-wide.xlsx
+++ b/outputs_xlsx_solution/test_1.1-wide.xlsx
@@ -147,6 +147,12 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -1087,10 +1093,26 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
